--- a/src/staticfiles/study/templates/event_form_bindings_import_template.xlsx
+++ b/src/staticfiles/study/templates/event_form_bindings_import_template.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,260 @@
           <t>Entry Mode</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Display Label Enabled</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Display Label Max Length</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Display Label Use Choice Label</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Display Label Empty Value Policy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Display Label Template VI</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Display Label Fallback Template VI</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Display Label Empty Text VI</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Display Label Template EN</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Display Label Fallback Template EN</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Display Label Empty Text EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>INVESTIGATOR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>120</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>AE #{{repeat_index}} - {{field:AE_TERM}}</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>{{form_name}} #{{repeat_index}}</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>AE #{{repeat_index}} - {{field:AE_TERM}}</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{{form_name}} #{{repeat_index}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INVESTIGATOR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>120</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CM #{{repeat_index}} - {{field:MED_NAME}}</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>{{form_name}} #{{repeat_index}}</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>CM #{{repeat_index}} - {{field:MED_NAME}}</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{{form_name}} #{{repeat_index}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SAE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>INVESTIGATOR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>120</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SAE #{{repeat_index}} - {{field:SAE_REPORT_NO}}</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>{{form_name}} #{{repeat_index}}</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SAE #{{repeat_index}} - {{field:SAE_REPORT_NO}}</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{{form_name}} #{{repeat_index}}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
